--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:12:06+00:00</t>
+    <t>2026-07-09T18:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:49:58+00:00</t>
+    <t>2026-07-19T17:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="116">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,10 @@
 </t>
   </si>
   <si>
-    <t>Transaction ExportArchivePortabilite</t>
+    <t>Archive stockant les données transverses associés au praticien et/ou au cabinet.</t>
+  </si>
+  <si>
+    <t>Transaction ExportArchivePortabilite.</t>
   </si>
   <si>
     <t>Base</t>
@@ -263,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>Informations éditoriales et instructions d'exploitation de l'archive</t>
+    <t>Informations éditoriales et instructions d'exploitation de l'archive.</t>
   </si>
   <si>
     <t>pdlgc-archive-transverse.TRANSVERSE</t>
@@ -273,7 +276,7 @@
 </t>
   </si>
   <si>
-    <t>répertoire contenant les données du praticien et/ ou du cabinet</t>
+    <t>répertoire contenant les données du praticien et/ou du cabinet.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -356,14 +359,20 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.TRANSVERSE.documents</t>
+    <t>pdlgc-archive-transverse.TRANSVERSE.documentPivot</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/Document
 </t>
   </si>
   <si>
-    <t>Documents trasnverses associés au praticien et/ou au cabinet</t>
+    <t>Données structurées du périmètre pivot relative au praticien et/ou au cabinet. Leur export est obligatoire.</t>
+  </si>
+  <si>
+    <t>pdlgc-archive-transverse.TRANSVERSE.documentHorsPivot</t>
+  </si>
+  <si>
+    <t>Données structurées hors périmètre pivot. Leur export est facultatif.</t>
   </si>
 </sst>
 </file>
@@ -665,11 +674,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.1953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.1953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.37890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.37890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -699,7 +708,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.69921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="47.37890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -846,13 +855,13 @@
         <v>76</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -902,7 +911,7 @@
         <v>73</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>74</v>
@@ -919,10 +928,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -930,10 +939,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>73</v>
@@ -945,13 +954,13 @@
         <v>73</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1002,13 +1011,13 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -1019,10 +1028,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1030,10 +1039,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -1045,13 +1054,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1102,27 +1111,27 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1133,7 +1142,7 @@
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1145,13 +1154,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1202,13 +1211,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1219,14 +1228,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1245,16 +1254,16 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1292,19 +1301,19 @@
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1316,19 +1325,19 @@
         <v>73</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1341,25 +1350,25 @@
         <v>73</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>73</v>
@@ -1408,7 +1417,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1420,15 +1429,15 @@
         <v>73</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1436,7 +1445,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>75</v>
@@ -1451,13 +1460,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1508,10 +1517,10 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>75</v>
@@ -1520,6 +1529,106 @@
         <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,7 +256,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.README</t>
+    <t>pdlgc-archive-transverse.readme</t>
   </si>
   <si>
     <t>1</t>
@@ -269,7 +269,7 @@
     <t>Informations éditoriales et instructions d'exploitation de l'archive.</t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.TRANSVERSE</t>
+    <t>pdlgc-archive-transverse.Transverse</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -283,7 +283,7 @@
 </t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.TRANSVERSE.id</t>
+    <t>pdlgc-archive-transverse.Transverse.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -299,7 +299,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.TRANSVERSE.extension</t>
+    <t>pdlgc-archive-transverse.Transverse.extension</t>
   </si>
   <si>
     <t>extensions
@@ -336,7 +336,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.TRANSVERSE.modifierExtension</t>
+    <t>pdlgc-archive-transverse.Transverse.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -359,7 +359,7 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.TRANSVERSE.documentPivot</t>
+    <t>pdlgc-archive-transverse.Transverse.documentPivot</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/Document
@@ -369,7 +369,7 @@
     <t>Données structurées du périmètre pivot relative au praticien et/ou au cabinet. Leur export est obligatoire.</t>
   </si>
   <si>
-    <t>pdlgc-archive-transverse.TRANSVERSE.documentHorsPivot</t>
+    <t>pdlgc-archive-transverse.Transverse.documentHorsPivot</t>
   </si>
   <si>
     <t>Données structurées hors périmètre pivot. Leur export est facultatif.</t>
@@ -677,8 +677,8 @@
   <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.37890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.37890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.640625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -708,7 +708,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="47.37890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.640625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-archive-transverse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
